--- a/305 - Research Project/05-research-data-and-analysis/04-descriptive-analysis/descriptive-analysis-workbook.xlsx
+++ b/305 - Research Project/05-research-data-and-analysis/04-descriptive-analysis/descriptive-analysis-workbook.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" r:id="Rceaac24653ea49c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligible Data" sheetId="2" r:id="Rfcd037692a574d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligibility Audit" sheetId="3" r:id="Rfe0822d60846448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="4" r:id="R9f5b789e5d5843e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile Tables" sheetId="5" r:id="R1179218c50c84ce6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Construct Summary" sheetId="6" r:id="Re109ffc61fc1444f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Summary" sheetId="7" r:id="Rc097977aecaf49f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Frequencies" sheetId="8" r:id="R00797e905b7b4c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" r:id="Rda8b5816fcc34914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligible Data" sheetId="2" r:id="Re17067a735cb45aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligibility Audit" sheetId="3" r:id="Re502a1cb4669402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codebook" sheetId="4" r:id="R37d1c8c9919a4b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile Tables" sheetId="5" r:id="Rc5e8324e886b4928"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Construct Summary" sheetId="6" r:id="R552dad2fd1fd4ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Summary" sheetId="7" r:id="Rb7fa98ba549c44a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Item Frequencies" sheetId="8" r:id="R2e23488a6dd94f0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -864,7 +864,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R47ffe618c62f437b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7aa619cd92904424"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -894,7 +894,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91b9192e75024f37"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23d8e3cb8dd344f8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -924,7 +924,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7b461201359f4cad"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbf9025f6c89748b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1252,7 +1252,7 @@
         <x:v>Processing note</x:v>
       </x:c>
       <x:c r="B8" s="25" t="str">
-        <x:v>Two approved item imputations are retained; profile blanks remain missing</x:v>
+        <x:v>Two approved item replacements are retained; profile blanks remain missing</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -9663,42 +9663,44 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="44" t="str">
-        <x:v>Manual-25</x:v>
+        <x:v>Manual-27</x:v>
       </x:c>
       <x:c r="B72" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
-      <x:c r="C72" s="44" t="str"/>
+      <x:c r="C72" s="44" t="str">
+        <x:v>45–54</x:v>
+      </x:c>
       <x:c r="D72" s="44" t="str">
-        <x:v>Above 20 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E72" s="44" t="str">
         <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F72" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G72" s="45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H72" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I72" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J72" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K72" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L72" s="46" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="M72" s="46" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M72" s="46" t="n">
-        <x:v>3.333</x:v>
-      </x:c>
       <x:c r="N72" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -9712,7 +9714,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="R72" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S72" s="46" t="n">
         <x:v>4</x:v>
@@ -9727,7 +9729,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="W72" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X72" s="46" t="n">
         <x:v>4</x:v>
@@ -9736,7 +9738,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Z72" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA72" s="46" t="n">
         <x:v>4</x:v>
@@ -9751,7 +9753,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AE72" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF72" s="46" t="n">
         <x:v>4</x:v>
@@ -9761,36 +9763,36 @@
       </x:c>
       <x:c r="AH72" s="46" t="n">
         <x:f>AVERAGE(H72:N72)</x:f>
-        <x:v>3.333285714285714</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AI72" s="46" t="n">
         <x:f>AVERAGE(O72:T72)</x:f>
-        <x:v>4</x:v>
+        <x:v>3.6666666666666665</x:v>
       </x:c>
       <x:c r="AJ72" s="46" t="n">
         <x:f>AVERAGE(U72:Z72)</x:f>
-        <x:v>3.8333333333333335</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK72" s="46" t="n">
         <x:f>AVERAGE(AA72:AG72)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.142857142857143</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="44" t="str">
-        <x:v>Manual-27</x:v>
+        <x:v>Manual-28</x:v>
       </x:c>
       <x:c r="B73" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C73" s="44" t="str">
-        <x:v>45–54</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D73" s="44" t="str">
         <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E73" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F73" s="45" t="n">
         <x:v>0</x:v>
@@ -9808,28 +9810,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K73" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M73" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R73" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S73" s="46" t="n">
         <x:v>4</x:v>
@@ -9841,7 +9843,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="V73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W73" s="46" t="n">
         <x:v>5</x:v>
@@ -9850,7 +9852,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Y73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z73" s="46" t="n">
         <x:v>5</x:v>
@@ -9859,13 +9861,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD73" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE73" s="46" t="n">
         <x:v>5</x:v>
@@ -9878,24 +9880,24 @@
       </x:c>
       <x:c r="AH73" s="46" t="n">
         <x:f>AVERAGE(H73:N73)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
       <x:c r="AI73" s="46" t="n">
         <x:f>AVERAGE(O73:T73)</x:f>
-        <x:v>3.6666666666666665</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ73" s="46" t="n">
         <x:f>AVERAGE(U73:Z73)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>4.666666666666667</x:v>
       </x:c>
       <x:c r="AK73" s="46" t="n">
         <x:f>AVERAGE(AA73:AG73)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="44" t="str">
-        <x:v>Manual-28</x:v>
+        <x:v>Manual-29</x:v>
       </x:c>
       <x:c r="B74" s="44" t="str">
         <x:v>manual</x:v>
@@ -9907,7 +9909,7 @@
         <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E74" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F74" s="45" t="n">
         <x:v>0</x:v>
@@ -9916,7 +9918,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I74" s="46" t="n">
         <x:v>4</x:v>
@@ -9925,13 +9927,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L74" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N74" s="46" t="n">
         <x:v>5</x:v>
@@ -9943,22 +9945,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q74" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V74" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W74" s="46" t="n">
         <x:v>5</x:v>
@@ -9973,13 +9975,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AA74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB74" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC74" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD74" s="46" t="n">
         <x:v>5</x:v>
@@ -9991,15 +9993,15 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AG74" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH74" s="46" t="n">
         <x:f>AVERAGE(H74:N74)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
       <x:c r="AI74" s="46" t="n">
         <x:f>AVERAGE(O74:T74)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4.833333333333333</x:v>
       </x:c>
       <x:c r="AJ74" s="46" t="n">
         <x:f>AVERAGE(U74:Z74)</x:f>
@@ -10007,12 +10009,12 @@
       </x:c>
       <x:c r="AK74" s="46" t="n">
         <x:f>AVERAGE(AA74:AG74)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="44" t="str">
-        <x:v>Manual-29</x:v>
+        <x:v>Manual-30</x:v>
       </x:c>
       <x:c r="B75" s="44" t="str">
         <x:v>manual</x:v>
@@ -10021,10 +10023,10 @@
         <x:v>35–44</x:v>
       </x:c>
       <x:c r="D75" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E75" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F75" s="45" t="n">
         <x:v>0</x:v>
@@ -10033,13 +10035,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I75" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K75" s="46" t="n">
         <x:v>5</x:v>
@@ -10054,49 +10056,49 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="O75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P75" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q75" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R75" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="S75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U75" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="V75" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X75" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="Y75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA75" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB75" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC75" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD75" s="46" t="n">
         <x:v>5</x:v>
@@ -10105,43 +10107,43 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF75" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG75" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AH75" s="46" t="n">
         <x:f>AVERAGE(H75:N75)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
       <x:c r="AI75" s="46" t="n">
         <x:f>AVERAGE(O75:T75)</x:f>
-        <x:v>4.833333333333333</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ75" s="46" t="n">
         <x:f>AVERAGE(U75:Z75)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK75" s="46" t="n">
         <x:f>AVERAGE(AA75:AG75)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.857142857142857</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="44" t="str">
-        <x:v>Manual-30</x:v>
+        <x:v>Manual-31</x:v>
       </x:c>
       <x:c r="B76" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C76" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D76" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E76" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F76" s="45" t="n">
         <x:v>0</x:v>
@@ -10150,7 +10152,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I76" s="46" t="n">
         <x:v>4</x:v>
@@ -10162,7 +10164,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M76" s="46" t="n">
         <x:v>5</x:v>
@@ -10174,13 +10176,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P76" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q76" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R76" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S76" s="46" t="n">
         <x:v>4</x:v>
@@ -10195,19 +10197,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="W76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA76" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB76" s="46" t="n">
         <x:v>5</x:v>
@@ -10229,36 +10231,36 @@
       </x:c>
       <x:c r="AH76" s="46" t="n">
         <x:f>AVERAGE(H76:N76)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
       <x:c r="AI76" s="46" t="n">
         <x:f>AVERAGE(O76:T76)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AJ76" s="46" t="n">
         <x:f>AVERAGE(U76:Z76)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK76" s="46" t="n">
         <x:f>AVERAGE(AA76:AG76)</x:f>
-        <x:v>4.857142857142857</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="44" t="str">
-        <x:v>Manual-31</x:v>
+        <x:v>Manual-33</x:v>
       </x:c>
       <x:c r="B77" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C77" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D77" s="44" t="str">
         <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E77" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Managerial</x:v>
       </x:c>
       <x:c r="F77" s="45" t="n">
         <x:v>0</x:v>
@@ -10270,10 +10272,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I77" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J77" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K77" s="46" t="n">
         <x:v>5</x:v>
@@ -10291,7 +10293,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P77" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q77" s="46" t="n">
         <x:v>4</x:v>
@@ -10306,64 +10308,64 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="U77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG77" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH77" s="46" t="n">
         <x:f>AVERAGE(H77:N77)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI77" s="46" t="n">
         <x:f>AVERAGE(O77:T77)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.166666666666667</x:v>
       </x:c>
       <x:c r="AJ77" s="46" t="n">
         <x:f>AVERAGE(U77:Z77)</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AK77" s="46" t="n">
         <x:f>AVERAGE(AA77:AG77)</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="44" t="str">
-        <x:v>Manual-33</x:v>
+        <x:v>Manual-35</x:v>
       </x:c>
       <x:c r="B78" s="44" t="str">
         <x:v>manual</x:v>
@@ -10375,7 +10377,7 @@
         <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E78" s="44" t="str">
-        <x:v>Managerial</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F78" s="45" t="n">
         <x:v>0</x:v>
@@ -10384,31 +10386,31 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O78" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P78" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q78" s="46" t="n">
         <x:v>4</x:v>
@@ -10417,10 +10419,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S78" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="T78" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="U78" s="46" t="n">
         <x:v>4</x:v>
@@ -10435,7 +10437,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Y78" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z78" s="46" t="n">
         <x:v>4</x:v>
@@ -10447,7 +10449,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AC78" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD78" s="46" t="n">
         <x:v>4</x:v>
@@ -10463,24 +10465,24 @@
       </x:c>
       <x:c r="AH78" s="46" t="n">
         <x:f>AVERAGE(H78:N78)</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AI78" s="46" t="n">
         <x:f>AVERAGE(O78:T78)</x:f>
-        <x:v>4.166666666666667</x:v>
+        <x:v>3.6666666666666665</x:v>
       </x:c>
       <x:c r="AJ78" s="46" t="n">
         <x:f>AVERAGE(U78:Z78)</x:f>
-        <x:v>4</x:v>
+        <x:v>3.8333333333333335</x:v>
       </x:c>
       <x:c r="AK78" s="46" t="n">
         <x:f>AVERAGE(AA78:AG78)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.142857142857143</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="44" t="str">
-        <x:v>Manual-35</x:v>
+        <x:v>Manual-36</x:v>
       </x:c>
       <x:c r="B79" s="44" t="str">
         <x:v>manual</x:v>
@@ -10489,7 +10491,7 @@
         <x:v>35–44</x:v>
       </x:c>
       <x:c r="D79" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E79" s="44" t="str">
         <x:v>Officer</x:v>
@@ -10501,115 +10503,115 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P79" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S79" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T79" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y79" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC79" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AD79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG79" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH79" s="46" t="n">
         <x:f>AVERAGE(H79:N79)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI79" s="46" t="n">
         <x:f>AVERAGE(O79:T79)</x:f>
-        <x:v>3.6666666666666665</x:v>
+        <x:v>4.833333333333333</x:v>
       </x:c>
       <x:c r="AJ79" s="46" t="n">
         <x:f>AVERAGE(U79:Z79)</x:f>
-        <x:v>3.8333333333333335</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK79" s="46" t="n">
         <x:f>AVERAGE(AA79:AG79)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="44" t="str">
-        <x:v>Manual-36</x:v>
+        <x:v>Manual-38</x:v>
       </x:c>
       <x:c r="B80" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C80" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>55 and above</x:v>
       </x:c>
       <x:c r="D80" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E80" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Managerial</x:v>
       </x:c>
       <x:c r="F80" s="45" t="n">
         <x:v>0</x:v>
@@ -10627,7 +10629,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L80" s="46" t="n">
         <x:v>5</x:v>
@@ -10642,7 +10644,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="P80" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q80" s="46" t="n">
         <x:v>5</x:v>
@@ -10660,13 +10662,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="V80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y80" s="46" t="n">
         <x:v>5</x:v>
@@ -10684,45 +10686,49 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AD80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF80" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG80" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AH80" s="46" t="n">
         <x:f>AVERAGE(H80:N80)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.857142857142857</x:v>
       </x:c>
       <x:c r="AI80" s="46" t="n">
         <x:f>AVERAGE(O80:T80)</x:f>
-        <x:v>4.833333333333333</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ80" s="46" t="n">
         <x:f>AVERAGE(U80:Z80)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AK80" s="46" t="n">
         <x:f>AVERAGE(AA80:AG80)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="44" t="str">
-        <x:v>Manual-37</x:v>
+        <x:v>Manual-39</x:v>
       </x:c>
       <x:c r="B81" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
-      <x:c r="C81" s="44" t="str"/>
-      <x:c r="D81" s="44" t="str"/>
+      <x:c r="C81" s="44" t="str">
+        <x:v>35–44</x:v>
+      </x:c>
+      <x:c r="D81" s="44" t="str">
+        <x:v>11–20 years</x:v>
+      </x:c>
       <x:c r="E81" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F81" s="45" t="n">
         <x:v>0</x:v>
@@ -10734,22 +10740,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J81" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L81" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O81" s="46" t="n">
         <x:v>5</x:v>
@@ -10758,16 +10764,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q81" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R81" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="S81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T81" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U81" s="46" t="n">
         <x:v>5</x:v>
@@ -10791,7 +10797,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AB81" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC81" s="46" t="n">
         <x:v>5</x:v>
@@ -10803,18 +10809,18 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AF81" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG81" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH81" s="46" t="n">
         <x:f>AVERAGE(H81:N81)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
       <x:c r="AI81" s="46" t="n">
         <x:f>AVERAGE(O81:T81)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ81" s="46" t="n">
         <x:f>AVERAGE(U81:Z81)</x:f>
@@ -10822,24 +10828,24 @@
       </x:c>
       <x:c r="AK81" s="46" t="n">
         <x:f>AVERAGE(AA81:AG81)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="44" t="str">
-        <x:v>Manual-38</x:v>
+        <x:v>Manual-41</x:v>
       </x:c>
       <x:c r="B82" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C82" s="44" t="str">
-        <x:v>55 and above</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D82" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>Below 5 years</x:v>
       </x:c>
       <x:c r="E82" s="44" t="str">
-        <x:v>Managerial</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F82" s="45" t="n">
         <x:v>0</x:v>
@@ -10854,10 +10860,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J82" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K82" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L82" s="46" t="n">
         <x:v>5</x:v>
@@ -10869,10 +10875,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="O82" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P82" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q82" s="46" t="n">
         <x:v>5</x:v>
@@ -10887,7 +10893,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="U82" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V82" s="46" t="n">
         <x:v>4</x:v>
@@ -10896,7 +10902,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="X82" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y82" s="46" t="n">
         <x:v>5</x:v>
@@ -10914,13 +10920,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AD82" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE82" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF82" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG82" s="46" t="n">
         <x:v>5</x:v>
@@ -10931,7 +10937,7 @@
       </x:c>
       <x:c r="AI82" s="46" t="n">
         <x:f>AVERAGE(O82:T82)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.666666666666667</x:v>
       </x:c>
       <x:c r="AJ82" s="46" t="n">
         <x:f>AVERAGE(U82:Z82)</x:f>
@@ -10939,24 +10945,24 @@
       </x:c>
       <x:c r="AK82" s="46" t="n">
         <x:f>AVERAGE(AA82:AG82)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="44" t="str">
-        <x:v>Manual-39</x:v>
+        <x:v>Manual-42</x:v>
       </x:c>
       <x:c r="B83" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C83" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D83" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E83" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F83" s="45" t="n">
         <x:v>0</x:v>
@@ -10968,22 +10974,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J83" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O83" s="46" t="n">
         <x:v>5</x:v>
@@ -10995,13 +11001,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="R83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T83" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U83" s="46" t="n">
         <x:v>5</x:v>
@@ -11013,16 +11019,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="X83" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y83" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z83" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AA83" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB83" s="46" t="n">
         <x:v>5</x:v>
@@ -11034,7 +11040,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AE83" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF83" s="46" t="n">
         <x:v>5</x:v>
@@ -11044,57 +11050,57 @@
       </x:c>
       <x:c r="AH83" s="46" t="n">
         <x:f>AVERAGE(H83:N83)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI83" s="46" t="n">
         <x:f>AVERAGE(O83:T83)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ83" s="46" t="n">
         <x:f>AVERAGE(U83:Z83)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.666666666666667</x:v>
       </x:c>
       <x:c r="AK83" s="46" t="n">
         <x:f>AVERAGE(AA83:AG83)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="44" t="str">
-        <x:v>Manual-41</x:v>
+        <x:v>Manual-46</x:v>
       </x:c>
       <x:c r="B84" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C84" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D84" s="44" t="str">
-        <x:v>Below 5 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E84" s="44" t="str">
         <x:v>Officer</x:v>
       </x:c>
       <x:c r="F84" s="45" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G84" s="45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J84" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M84" s="46" t="n">
         <x:v>5</x:v>
@@ -11109,76 +11115,76 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="T84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U84" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="V84" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W84" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="X84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Y84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AG84" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AH84" s="46" t="n">
         <x:f>AVERAGE(H84:N84)</x:f>
-        <x:v>4.857142857142857</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AI84" s="46" t="n">
         <x:f>AVERAGE(O84:T84)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>3.8333333333333335</x:v>
       </x:c>
       <x:c r="AJ84" s="46" t="n">
         <x:f>AVERAGE(U84:Z84)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>3.1666666666666665</x:v>
       </x:c>
       <x:c r="AK84" s="46" t="n">
         <x:f>AVERAGE(AA84:AG84)</x:f>
-        <x:v>5</x:v>
+        <x:v>3.7142857142857144</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="44" t="str">
-        <x:v>Manual-42</x:v>
+        <x:v>Manual-47</x:v>
       </x:c>
       <x:c r="B85" s="44" t="str">
         <x:v>manual</x:v>
@@ -11190,7 +11196,7 @@
         <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E85" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F85" s="45" t="n">
         <x:v>0</x:v>
@@ -11199,13 +11205,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K85" s="46" t="n">
         <x:v>5</x:v>
@@ -11214,37 +11220,37 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O85" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="P85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X85" s="46" t="n">
         <x:v>4</x:v>
@@ -11253,55 +11259,55 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Z85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA85" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE85" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AF85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG85" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH85" s="46" t="n">
         <x:f>AVERAGE(H85:N85)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
       <x:c r="AI85" s="46" t="n">
         <x:f>AVERAGE(O85:T85)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.166666666666667</x:v>
       </x:c>
       <x:c r="AJ85" s="46" t="n">
         <x:f>AVERAGE(U85:Z85)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AK85" s="46" t="n">
         <x:f>AVERAGE(AA85:AG85)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.142857142857143</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="44" t="str">
-        <x:v>Manual-46</x:v>
+        <x:v>Manual-48</x:v>
       </x:c>
       <x:c r="B86" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C86" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D86" s="44" t="str">
         <x:v>5–10 years</x:v>
@@ -11310,7 +11316,7 @@
         <x:v>Officer</x:v>
       </x:c>
       <x:c r="F86" s="45" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G86" s="45" t="n">
         <x:v>0</x:v>
@@ -11322,19 +11328,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J86" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K86" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L86" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M86" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N86" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O86" s="46" t="n">
         <x:v>4</x:v>
@@ -11349,40 +11355,40 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S86" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T86" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="U86" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V86" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W86" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X86" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y86" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z86" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA86" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB86" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AC86" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD86" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AE86" s="46" t="n">
         <x:v>4</x:v>
@@ -11395,36 +11401,36 @@
       </x:c>
       <x:c r="AH86" s="46" t="n">
         <x:f>AVERAGE(H86:N86)</x:f>
-        <x:v>4</x:v>
+        <x:v>3.7142857142857144</x:v>
       </x:c>
       <x:c r="AI86" s="46" t="n">
         <x:f>AVERAGE(O86:T86)</x:f>
-        <x:v>3.8333333333333335</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AJ86" s="46" t="n">
         <x:f>AVERAGE(U86:Z86)</x:f>
-        <x:v>3.1666666666666665</x:v>
+        <x:v>3.6666666666666665</x:v>
       </x:c>
       <x:c r="AK86" s="46" t="n">
         <x:f>AVERAGE(AA86:AG86)</x:f>
-        <x:v>3.7142857142857144</x:v>
+        <x:v>3.4285714285714284</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="44" t="str">
-        <x:v>Manual-47</x:v>
+        <x:v>Manual-50</x:v>
       </x:c>
       <x:c r="B87" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C87" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>55 and above</x:v>
       </x:c>
       <x:c r="D87" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E87" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Managerial</x:v>
       </x:c>
       <x:c r="F87" s="45" t="n">
         <x:v>0</x:v>
@@ -11445,16 +11451,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L87" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O87" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P87" s="46" t="n">
         <x:v>4</x:v>
@@ -11469,13 +11475,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="W87" s="46" t="n">
         <x:v>4</x:v>
@@ -11490,13 +11496,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AA87" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AC87" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD87" s="46" t="n">
         <x:v>4</x:v>
@@ -11512,7 +11518,7 @@
       </x:c>
       <x:c r="AH87" s="46" t="n">
         <x:f>AVERAGE(H87:N87)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
       <x:c r="AI87" s="46" t="n">
         <x:f>AVERAGE(O87:T87)</x:f>
@@ -11520,16 +11526,16 @@
       </x:c>
       <x:c r="AJ87" s="46" t="n">
         <x:f>AVERAGE(U87:Z87)</x:f>
-        <x:v>4</x:v>
+        <x:v>3.6666666666666665</x:v>
       </x:c>
       <x:c r="AK87" s="46" t="n">
         <x:f>AVERAGE(AA87:AG87)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>3.7142857142857144</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="44" t="str">
-        <x:v>Manual-48</x:v>
+        <x:v>Manual-51</x:v>
       </x:c>
       <x:c r="B88" s="44" t="str">
         <x:v>manual</x:v>
@@ -11538,7 +11544,7 @@
         <x:v>35–44</x:v>
       </x:c>
       <x:c r="D88" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E88" s="44" t="str">
         <x:v>Officer</x:v>
@@ -11550,112 +11556,112 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE88" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG88" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH88" s="46" t="n">
         <x:f>AVERAGE(H88:N88)</x:f>
-        <x:v>3.7142857142857144</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI88" s="46" t="n">
         <x:f>AVERAGE(O88:T88)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ88" s="46" t="n">
         <x:f>AVERAGE(U88:Z88)</x:f>
-        <x:v>3.6666666666666665</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK88" s="46" t="n">
         <x:f>AVERAGE(AA88:AG88)</x:f>
-        <x:v>3.4285714285714284</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="44" t="str">
-        <x:v>Manual-50</x:v>
+        <x:v>Manual-52</x:v>
       </x:c>
       <x:c r="B89" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C89" s="44" t="str">
-        <x:v>55 and above</x:v>
+        <x:v>45–54</x:v>
       </x:c>
       <x:c r="D89" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>Above 20 years</x:v>
       </x:c>
       <x:c r="E89" s="44" t="str">
         <x:v>Managerial</x:v>
@@ -11667,19 +11673,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K89" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="L89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M89" s="46" t="n">
         <x:v>5</x:v>
@@ -11688,82 +11694,82 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="O89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T89" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="U89" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V89" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB89" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC89" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG89" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH89" s="46" t="n">
         <x:f>AVERAGE(H89:N89)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI89" s="46" t="n">
         <x:f>AVERAGE(O89:T89)</x:f>
-        <x:v>4.166666666666667</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ89" s="46" t="n">
         <x:f>AVERAGE(U89:Z89)</x:f>
-        <x:v>3.6666666666666665</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK89" s="46" t="n">
         <x:f>AVERAGE(AA89:AG89)</x:f>
-        <x:v>3.7142857142857144</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="44" t="str">
-        <x:v>Manual-51</x:v>
+        <x:v>Manual-53</x:v>
       </x:c>
       <x:c r="B90" s="44" t="str">
         <x:v>manual</x:v>
@@ -11880,19 +11886,19 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="44" t="str">
-        <x:v>Manual-52</x:v>
+        <x:v>Manual-54</x:v>
       </x:c>
       <x:c r="B91" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C91" s="44" t="str">
-        <x:v>45–54</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D91" s="44" t="str">
-        <x:v>Above 20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E91" s="44" t="str">
-        <x:v>Managerial</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F91" s="45" t="n">
         <x:v>0</x:v>
@@ -11907,7 +11913,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K91" s="46" t="n">
         <x:v>5</x:v>
@@ -11919,13 +11925,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="N91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q91" s="46" t="n">
         <x:v>5</x:v>
@@ -11934,40 +11940,40 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="S91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE91" s="46" t="n">
         <x:v>5</x:v>
@@ -11976,37 +11982,37 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AG91" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH91" s="46" t="n">
         <x:f>AVERAGE(H91:N91)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
       <x:c r="AI91" s="46" t="n">
         <x:f>AVERAGE(O91:T91)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AJ91" s="46" t="n">
         <x:f>AVERAGE(U91:Z91)</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AK91" s="46" t="n">
         <x:f>AVERAGE(AA91:AG91)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="44" t="str">
-        <x:v>Manual-53</x:v>
+        <x:v>Manual-55</x:v>
       </x:c>
       <x:c r="B92" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C92" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>45–54</x:v>
       </x:c>
       <x:c r="D92" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>Above 20 years</x:v>
       </x:c>
       <x:c r="E92" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12021,67 +12027,67 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="Q92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="T92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="V92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="Y92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB92" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AC92" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD92" s="46" t="n">
         <x:v>5</x:v>
@@ -12097,24 +12103,24 @@
       </x:c>
       <x:c r="AH92" s="46" t="n">
         <x:f>AVERAGE(H92:N92)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
       <x:c r="AI92" s="46" t="n">
         <x:f>AVERAGE(O92:T92)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AJ92" s="46" t="n">
         <x:f>AVERAGE(U92:Z92)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK92" s="46" t="n">
         <x:f>AVERAGE(AA92:AG92)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="44" t="str">
-        <x:v>Manual-54</x:v>
+        <x:v>Manual-56</x:v>
       </x:c>
       <x:c r="B93" s="44" t="str">
         <x:v>manual</x:v>
@@ -12123,7 +12129,7 @@
         <x:v>25–34</x:v>
       </x:c>
       <x:c r="D93" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>Below 5 years</x:v>
       </x:c>
       <x:c r="E93" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12135,25 +12141,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="O93" s="46" t="n">
         <x:v>4</x:v>
@@ -12162,16 +12168,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S93" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="T93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="U93" s="46" t="n">
         <x:v>4</x:v>
@@ -12195,30 +12201,30 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AC93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AD93" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AE93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AF93" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AG93" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AH93" s="46" t="n">
         <x:f>AVERAGE(H93:N93)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>2.857142857142857</x:v>
       </x:c>
       <x:c r="AI93" s="46" t="n">
         <x:f>AVERAGE(O93:T93)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>3.5</x:v>
       </x:c>
       <x:c r="AJ93" s="46" t="n">
         <x:f>AVERAGE(U93:Z93)</x:f>
@@ -12226,21 +12232,21 @@
       </x:c>
       <x:c r="AK93" s="46" t="n">
         <x:f>AVERAGE(AA93:AG93)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>2.7142857142857144</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="44" t="str">
-        <x:v>Manual-55</x:v>
+        <x:v>Manual-57</x:v>
       </x:c>
       <x:c r="B94" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C94" s="44" t="str">
-        <x:v>45–54</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D94" s="44" t="str">
-        <x:v>Above 20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E94" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12252,28 +12258,28 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I94" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P94" s="46" t="n">
         <x:v>5</x:v>
@@ -12282,10 +12288,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="R94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T94" s="46" t="n">
         <x:v>4</x:v>
@@ -12294,7 +12300,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="V94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W94" s="46" t="n">
         <x:v>4</x:v>
@@ -12309,55 +12315,55 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AA94" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC94" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG94" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH94" s="46" t="n">
         <x:f>AVERAGE(H94:N94)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
       <x:c r="AI94" s="46" t="n">
         <x:f>AVERAGE(O94:T94)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ94" s="46" t="n">
         <x:f>AVERAGE(U94:Z94)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AK94" s="46" t="n">
         <x:f>AVERAGE(AA94:AG94)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.142857142857143</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="44" t="str">
-        <x:v>Manual-56</x:v>
+        <x:v>Manual-58</x:v>
       </x:c>
       <x:c r="B95" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C95" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D95" s="44" t="str">
-        <x:v>Below 5 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E95" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12369,112 +12375,112 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H95" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J95" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K95" s="46" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K95" s="46" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="L95" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M95" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N95" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O95" s="46" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M95" s="46" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="N95" s="46" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="O95" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="P95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="Q95" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="S95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="T95" s="46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U95" s="46" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="U95" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="V95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y95" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="Z95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA95" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB95" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AC95" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AD95" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE95" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF95" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG95" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH95" s="46" t="n">
         <x:f>AVERAGE(H95:N95)</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>1.4285714285714286</x:v>
       </x:c>
       <x:c r="AI95" s="46" t="n">
         <x:f>AVERAGE(O95:T95)</x:f>
-        <x:v>3.5</x:v>
+        <x:v>1.6666666666666667</x:v>
       </x:c>
       <x:c r="AJ95" s="46" t="n">
         <x:f>AVERAGE(U95:Z95)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK95" s="46" t="n">
         <x:f>AVERAGE(AA95:AG95)</x:f>
-        <x:v>2.7142857142857144</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="44" t="str">
-        <x:v>Manual-57</x:v>
+        <x:v>Manual-60</x:v>
       </x:c>
       <x:c r="B96" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C96" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D96" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E96" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12489,34 +12495,34 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I96" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J96" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="L96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q96" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="R96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S96" s="46" t="n">
         <x:v>4</x:v>
@@ -12528,13 +12534,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="V96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W96" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="X96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y96" s="46" t="n">
         <x:v>4</x:v>
@@ -12543,7 +12549,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AA96" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB96" s="46" t="n">
         <x:v>4</x:v>
@@ -12552,7 +12558,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD96" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE96" s="46" t="n">
         <x:v>4</x:v>
@@ -12565,15 +12571,15 @@
       </x:c>
       <x:c r="AH96" s="46" t="n">
         <x:f>AVERAGE(H96:N96)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>3.5714285714285716</x:v>
       </x:c>
       <x:c r="AI96" s="46" t="n">
         <x:f>AVERAGE(O96:T96)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AJ96" s="46" t="n">
         <x:f>AVERAGE(U96:Z96)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4.166666666666667</x:v>
       </x:c>
       <x:c r="AK96" s="46" t="n">
         <x:f>AVERAGE(AA96:AG96)</x:f>
@@ -12582,7 +12588,7 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="44" t="str">
-        <x:v>Manual-58</x:v>
+        <x:v>Manual-62</x:v>
       </x:c>
       <x:c r="B97" s="44" t="str">
         <x:v>manual</x:v>
@@ -12603,61 +12609,61 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="M97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T97" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U97" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Y97" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AA97" s="46" t="n">
         <x:v>4</x:v>
@@ -12669,49 +12675,49 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF97" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AG97" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH97" s="46" t="n">
         <x:f>AVERAGE(H97:N97)</x:f>
-        <x:v>1.4285714285714286</x:v>
+        <x:v>3.857142857142857</x:v>
       </x:c>
       <x:c r="AI97" s="46" t="n">
         <x:f>AVERAGE(O97:T97)</x:f>
-        <x:v>1.6666666666666667</x:v>
+        <x:v>3.8333333333333335</x:v>
       </x:c>
       <x:c r="AJ97" s="46" t="n">
         <x:f>AVERAGE(U97:Z97)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>3.8333333333333335</x:v>
       </x:c>
       <x:c r="AK97" s="46" t="n">
         <x:f>AVERAGE(AA97:AG97)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="44" t="str">
-        <x:v>Manual-60</x:v>
+        <x:v>Manual-63</x:v>
       </x:c>
       <x:c r="B98" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C98" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D98" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>Below 5 years</x:v>
       </x:c>
       <x:c r="E98" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F98" s="45" t="n">
         <x:v>0</x:v>
@@ -12723,19 +12729,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I98" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J98" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K98" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M98" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N98" s="46" t="n">
         <x:v>4</x:v>
@@ -12744,7 +12750,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q98" s="46" t="n">
         <x:v>4</x:v>
@@ -12753,70 +12759,70 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U98" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="V98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA98" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AB98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD98" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AE98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG98" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH98" s="46" t="n">
         <x:f>AVERAGE(H98:N98)</x:f>
-        <x:v>3.5714285714285716</x:v>
+        <x:v>3.2857142857142856</x:v>
       </x:c>
       <x:c r="AI98" s="46" t="n">
         <x:f>AVERAGE(O98:T98)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ98" s="46" t="n">
         <x:f>AVERAGE(U98:Z98)</x:f>
-        <x:v>4.166666666666667</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK98" s="46" t="n">
         <x:f>AVERAGE(AA98:AG98)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>4.857142857142857</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="44" t="str">
-        <x:v>Manual-62</x:v>
+        <x:v>Manual-64</x:v>
       </x:c>
       <x:c r="B99" s="44" t="str">
         <x:v>manual</x:v>
@@ -12825,7 +12831,7 @@
         <x:v>35–44</x:v>
       </x:c>
       <x:c r="D99" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>5–10 years</x:v>
       </x:c>
       <x:c r="E99" s="44" t="str">
         <x:v>Officer</x:v>
@@ -12840,16 +12846,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I99" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J99" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L99" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M99" s="46" t="n">
         <x:v>4</x:v>
@@ -12858,28 +12864,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="O99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P99" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q99" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S99" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="T99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U99" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="V99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W99" s="46" t="n">
         <x:v>4</x:v>
@@ -12888,7 +12894,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Y99" s="46" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z99" s="46" t="n">
         <x:v>4</x:v>
@@ -12903,46 +12909,46 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AE99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF99" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AG99" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AH99" s="46" t="n">
         <x:f>AVERAGE(H99:N99)</x:f>
-        <x:v>3.857142857142857</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
       <x:c r="AI99" s="46" t="n">
         <x:f>AVERAGE(O99:T99)</x:f>
-        <x:v>3.8333333333333335</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AJ99" s="46" t="n">
         <x:f>AVERAGE(U99:Z99)</x:f>
-        <x:v>3.8333333333333335</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK99" s="46" t="n">
         <x:f>AVERAGE(AA99:AG99)</x:f>
-        <x:v>4</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="44" t="str">
-        <x:v>Manual-63</x:v>
+        <x:v>Manual-65</x:v>
       </x:c>
       <x:c r="B100" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C100" s="44" t="str">
-        <x:v>25–34</x:v>
+        <x:v>35–44</x:v>
       </x:c>
       <x:c r="D100" s="44" t="str">
-        <x:v>Below 5 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E100" s="44" t="str">
         <x:v>Clerical</x:v>
@@ -12954,10 +12960,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I100" s="46" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J100" s="46" t="n">
         <x:v>4</x:v>
@@ -12966,25 +12972,25 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="L100" s="46" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O100" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="P100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Q100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="S100" s="46" t="n">
         <x:v>5</x:v>
@@ -12993,25 +12999,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="U100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="V100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="W100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X100" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="Y100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z100" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AA100" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB100" s="46" t="n">
         <x:v>5</x:v>
@@ -13023,34 +13029,34 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AE100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AF100" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG100" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AH100" s="46" t="n">
         <x:f>AVERAGE(H100:N100)</x:f>
-        <x:v>3.2857142857142856</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
       <x:c r="AI100" s="46" t="n">
         <x:f>AVERAGE(O100:T100)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4.666666666666667</x:v>
       </x:c>
       <x:c r="AJ100" s="46" t="n">
         <x:f>AVERAGE(U100:Z100)</x:f>
-        <x:v>5</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AK100" s="46" t="n">
         <x:f>AVERAGE(AA100:AG100)</x:f>
-        <x:v>4.857142857142857</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="44" t="str">
-        <x:v>Manual-64</x:v>
+        <x:v>Manual-66</x:v>
       </x:c>
       <x:c r="B101" s="44" t="str">
         <x:v>manual</x:v>
@@ -13059,10 +13065,10 @@
         <x:v>35–44</x:v>
       </x:c>
       <x:c r="D101" s="44" t="str">
-        <x:v>5–10 years</x:v>
+        <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E101" s="44" t="str">
-        <x:v>Officer</x:v>
+        <x:v>Clerical</x:v>
       </x:c>
       <x:c r="F101" s="45" t="n">
         <x:v>0</x:v>
@@ -13071,7 +13077,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I101" s="46" t="n">
         <x:v>5</x:v>
@@ -13080,19 +13086,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K101" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="L101" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="M101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N101" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="O101" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="P101" s="46" t="n">
         <x:v>4</x:v>
@@ -13104,25 +13110,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="S101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T101" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="V101" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="W101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y101" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="Z101" s="46" t="n">
         <x:v>4</x:v>
@@ -13146,28 +13152,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AG101" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH101" s="46" t="n">
         <x:f>AVERAGE(H101:N101)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.428571428571429</x:v>
       </x:c>
       <x:c r="AI101" s="46" t="n">
         <x:f>AVERAGE(O101:T101)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4.333333333333333</x:v>
       </x:c>
       <x:c r="AJ101" s="46" t="n">
         <x:f>AVERAGE(U101:Z101)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>4.666666666666667</x:v>
       </x:c>
       <x:c r="AK101" s="46" t="n">
         <x:f>AVERAGE(AA101:AG101)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="44" t="str">
-        <x:v>Manual-65</x:v>
+        <x:v>Manual-67</x:v>
       </x:c>
       <x:c r="B102" s="44" t="str">
         <x:v>manual</x:v>
@@ -13179,7 +13185,7 @@
         <x:v>11–20 years</x:v>
       </x:c>
       <x:c r="E102" s="44" t="str">
-        <x:v>Clerical</x:v>
+        <x:v>Officer</x:v>
       </x:c>
       <x:c r="F102" s="45" t="n">
         <x:v>0</x:v>
@@ -13194,19 +13200,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J102" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K102" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="L102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="M102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="O102" s="46" t="n">
         <x:v>4</x:v>
@@ -13215,13 +13221,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="Q102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="R102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="S102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="T102" s="46" t="n">
         <x:v>5</x:v>
@@ -13239,13 +13245,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Y102" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z102" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="AA102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB102" s="46" t="n">
         <x:v>5</x:v>
@@ -13254,7 +13260,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AD102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AE102" s="46" t="n">
         <x:v>4</x:v>
@@ -13263,28 +13269,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AG102" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AH102" s="46" t="n">
         <x:f>AVERAGE(H102:N102)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
       <x:c r="AI102" s="46" t="n">
         <x:f>AVERAGE(O102:T102)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>4.166666666666667</x:v>
       </x:c>
       <x:c r="AJ102" s="46" t="n">
         <x:f>AVERAGE(U102:Z102)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="AK102" s="46" t="n">
         <x:f>AVERAGE(AA102:AG102)</x:f>
-        <x:v>4.714285714285714</x:v>
+        <x:v>4.285714285714286</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="44" t="str">
-        <x:v>Manual-66</x:v>
+        <x:v>Manual-68</x:v>
       </x:c>
       <x:c r="B103" s="44" t="str">
         <x:v>manual</x:v>
@@ -13311,28 +13317,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M103" s="46" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="N103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="O103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="P103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Q103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="R103" s="46" t="n">
         <x:v>5</x:v>
@@ -13341,7 +13347,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="T103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="U103" s="46" t="n">
         <x:v>5</x:v>
@@ -13356,19 +13362,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Y103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Z103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AA103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AB103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AC103" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AD103" s="46" t="n">
         <x:v>5</x:v>
@@ -13384,33 +13390,33 @@
       </x:c>
       <x:c r="AH103" s="46" t="n">
         <x:f>AVERAGE(H103:N103)</x:f>
-        <x:v>4.428571428571429</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AI103" s="46" t="n">
         <x:f>AVERAGE(O103:T103)</x:f>
-        <x:v>4.333333333333333</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AJ103" s="46" t="n">
         <x:f>AVERAGE(U103:Z103)</x:f>
-        <x:v>4.666666666666667</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AK103" s="46" t="n">
         <x:f>AVERAGE(AA103:AG103)</x:f>
-        <x:v>4.571428571428571</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="44" t="str">
-        <x:v>Manual-67</x:v>
+        <x:v>Manual-70</x:v>
       </x:c>
       <x:c r="B104" s="44" t="str">
         <x:v>manual</x:v>
       </x:c>
       <x:c r="C104" s="44" t="str">
-        <x:v>35–44</x:v>
+        <x:v>25–34</x:v>
       </x:c>
       <x:c r="D104" s="44" t="str">
-        <x:v>11–20 years</x:v>
+        <x:v>Below 5 years</x:v>
       </x:c>
       <x:c r="E104" s="44" t="str">
         <x:v>Officer</x:v>
@@ -13431,13 +13437,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="K104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="L104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="N104" s="46" t="n">
         <x:v>4</x:v>
@@ -13455,10 +13461,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="S104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="T104" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="U104" s="46" t="n">
         <x:v>4</x:v>
@@ -13473,7 +13479,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="Y104" s="46" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="Z104" s="46" t="n">
         <x:v>5</x:v>
@@ -13491,17 +13497,17 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AE104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AF104" s="46" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="AG104" s="46" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AH104" s="46" t="n">
         <x:f>AVERAGE(H104:N104)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.714285714285714</x:v>
       </x:c>
       <x:c r="AI104" s="46" t="n">
         <x:f>AVERAGE(O104:T104)</x:f>
@@ -13509,251 +13515,95 @@
       </x:c>
       <x:c r="AJ104" s="46" t="n">
         <x:f>AVERAGE(U104:Z104)</x:f>
-        <x:v>4.5</x:v>
+        <x:v>4.166666666666667</x:v>
       </x:c>
       <x:c r="AK104" s="46" t="n">
         <x:f>AVERAGE(AA104:AG104)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.571428571428571</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
-      <x:c r="A105" s="44" t="str">
-        <x:v>Manual-68</x:v>
-      </x:c>
-      <x:c r="B105" s="44" t="str">
-        <x:v>manual</x:v>
-      </x:c>
-      <x:c r="C105" s="44" t="str">
-        <x:v>35–44</x:v>
-      </x:c>
-      <x:c r="D105" s="44" t="str">
-        <x:v>11–20 years</x:v>
-      </x:c>
-      <x:c r="E105" s="44" t="str">
-        <x:v>Clerical</x:v>
-      </x:c>
-      <x:c r="F105" s="45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G105" s="45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="O105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="P105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Q105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="R105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="S105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="U105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="V105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="W105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="X105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Y105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Z105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AA105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AB105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AC105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AD105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AE105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AF105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AG105" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AH105" s="46" t="n">
-        <x:f>AVERAGE(H105:N105)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AI105" s="46" t="n">
-        <x:f>AVERAGE(O105:T105)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AJ105" s="46" t="n">
-        <x:f>AVERAGE(U105:Z105)</x:f>
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AK105" s="46" t="n">
-        <x:f>AVERAGE(AA105:AG105)</x:f>
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A105" s="44"/>
+      <x:c r="B105" s="44"/>
+      <x:c r="C105" s="44"/>
+      <x:c r="D105" s="44"/>
+      <x:c r="E105" s="44"/>
+      <x:c r="F105" s="45"/>
+      <x:c r="G105" s="45"/>
+      <x:c r="H105" s="46"/>
+      <x:c r="I105" s="46"/>
+      <x:c r="J105" s="46"/>
+      <x:c r="K105" s="46"/>
+      <x:c r="L105" s="46"/>
+      <x:c r="M105" s="46"/>
+      <x:c r="N105" s="46"/>
+      <x:c r="O105" s="46"/>
+      <x:c r="P105" s="46"/>
+      <x:c r="Q105" s="46"/>
+      <x:c r="R105" s="46"/>
+      <x:c r="S105" s="46"/>
+      <x:c r="T105" s="46"/>
+      <x:c r="U105" s="46"/>
+      <x:c r="V105" s="46"/>
+      <x:c r="W105" s="46"/>
+      <x:c r="X105" s="46"/>
+      <x:c r="Y105" s="46"/>
+      <x:c r="Z105" s="46"/>
+      <x:c r="AA105" s="46"/>
+      <x:c r="AB105" s="46"/>
+      <x:c r="AC105" s="46"/>
+      <x:c r="AD105" s="46"/>
+      <x:c r="AE105" s="46"/>
+      <x:c r="AF105" s="46"/>
+      <x:c r="AG105" s="46"/>
+      <x:c r="AH105" s="46"/>
+      <x:c r="AI105" s="46"/>
+      <x:c r="AJ105" s="46"/>
+      <x:c r="AK105" s="46"/>
     </x:row>
     <x:row r="106">
-      <x:c r="A106" s="44" t="str">
-        <x:v>Manual-70</x:v>
-      </x:c>
-      <x:c r="B106" s="44" t="str">
-        <x:v>manual</x:v>
-      </x:c>
-      <x:c r="C106" s="44" t="str">
-        <x:v>25–34</x:v>
-      </x:c>
-      <x:c r="D106" s="44" t="str">
-        <x:v>Below 5 years</x:v>
-      </x:c>
-      <x:c r="E106" s="44" t="str">
-        <x:v>Officer</x:v>
-      </x:c>
-      <x:c r="F106" s="45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G106" s="45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="M106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="O106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="P106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="Q106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="R106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="S106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="T106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="U106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="V106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="W106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="X106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="Y106" s="46" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="Z106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AA106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="AB106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AC106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AD106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="AE106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AF106" s="46" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="AG106" s="46" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AH106" s="46" t="n">
-        <x:f>AVERAGE(H106:N106)</x:f>
-        <x:v>4.714285714285714</x:v>
-      </x:c>
-      <x:c r="AI106" s="46" t="n">
-        <x:f>AVERAGE(O106:T106)</x:f>
-        <x:v>4.166666666666667</x:v>
-      </x:c>
-      <x:c r="AJ106" s="46" t="n">
-        <x:f>AVERAGE(U106:Z106)</x:f>
-        <x:v>4.166666666666667</x:v>
-      </x:c>
-      <x:c r="AK106" s="46" t="n">
-        <x:f>AVERAGE(AA106:AG106)</x:f>
-        <x:v>4.571428571428571</x:v>
-      </x:c>
+      <x:c r="A106" s="44"/>
+      <x:c r="B106" s="44"/>
+      <x:c r="C106" s="44"/>
+      <x:c r="D106" s="44"/>
+      <x:c r="E106" s="44"/>
+      <x:c r="F106" s="45"/>
+      <x:c r="G106" s="45"/>
+      <x:c r="H106" s="46"/>
+      <x:c r="I106" s="46"/>
+      <x:c r="J106" s="46"/>
+      <x:c r="K106" s="46"/>
+      <x:c r="L106" s="46"/>
+      <x:c r="M106" s="46"/>
+      <x:c r="N106" s="46"/>
+      <x:c r="O106" s="46"/>
+      <x:c r="P106" s="46"/>
+      <x:c r="Q106" s="46"/>
+      <x:c r="R106" s="46"/>
+      <x:c r="S106" s="46"/>
+      <x:c r="T106" s="46"/>
+      <x:c r="U106" s="46"/>
+      <x:c r="V106" s="46"/>
+      <x:c r="W106" s="46"/>
+      <x:c r="X106" s="46"/>
+      <x:c r="Y106" s="46"/>
+      <x:c r="Z106" s="46"/>
+      <x:c r="AA106" s="46"/>
+      <x:c r="AB106" s="46"/>
+      <x:c r="AC106" s="46"/>
+      <x:c r="AD106" s="46"/>
+      <x:c r="AE106" s="46"/>
+      <x:c r="AF106" s="46"/>
+      <x:c r="AG106" s="46"/>
+      <x:c r="AH106" s="46"/>
+      <x:c r="AI106" s="46"/>
+      <x:c r="AJ106" s="46"/>
+      <x:c r="AK106" s="46"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b165702157d404a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdeaceb722ada4fa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17972,7 +17822,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39b0d2de391f40f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87898fe103874ed2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18605,18 +18455,18 @@
       </x:c>
       <x:c r="H4" s="63" t="n">
         <x:f>G4/SUM($G$4:$G$7)</x:f>
-        <x:v>0.07692307692307693</x:v>
+        <x:v>0.07766990291262135</x:v>
       </x:c>
       <x:c r="K4" s="20" t="str">
         <x:v>Clerical</x:v>
       </x:c>
       <x:c r="L4" s="20" t="n">
         <x:f>COUNTIF('Eligible Data'!$E$2:$E$106,K4)</x:f>
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M4" s="63" t="n">
         <x:f>L4/SUM($L$4:$L$6)</x:f>
-        <x:v>0.20952380952380953</x:v>
+        <x:v>0.1941747572815534</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -18640,7 +18490,7 @@
       </x:c>
       <x:c r="H5" s="63" t="n">
         <x:f>G5/SUM($G$4:$G$7)</x:f>
-        <x:v>0.27884615384615385</x:v>
+        <x:v>0.2815533980582524</x:v>
       </x:c>
       <x:c r="K5" s="20" t="str">
         <x:v>Officer</x:v>
@@ -18651,7 +18501,7 @@
       </x:c>
       <x:c r="M5" s="63" t="n">
         <x:f>L5/SUM($L$4:$L$6)</x:f>
-        <x:v>0.5428571428571428</x:v>
+        <x:v>0.5533980582524272</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -18675,7 +18525,7 @@
       </x:c>
       <x:c r="H6" s="63" t="n">
         <x:f>G6/SUM($G$4:$G$7)</x:f>
-        <x:v>0.5384615384615384</x:v>
+        <x:v>0.5436893203883495</x:v>
       </x:c>
       <x:c r="K6" s="20" t="str">
         <x:v>Managerial</x:v>
@@ -18686,7 +18536,7 @@
       </x:c>
       <x:c r="M6" s="63" t="n">
         <x:f>L6/SUM($L$4:$L$6)</x:f>
-        <x:v>0.24761904761904763</x:v>
+        <x:v>0.2524271844660194</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -18706,22 +18556,22 @@
       </x:c>
       <x:c r="G7" s="20" t="n">
         <x:f>COUNTIF('Eligible Data'!$D$2:$D$106,F7)</x:f>
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="H7" s="63" t="n">
         <x:f>G7/SUM($G$4:$G$7)</x:f>
-        <x:v>0.10576923076923077</x:v>
+        <x:v>0.0970873786407767</x:v>
       </x:c>
       <x:c r="K7" s="20" t="str">
         <x:v>Missing</x:v>
       </x:c>
       <x:c r="L7" s="20" t="n">
         <x:f>COUNTBLANK('Eligible Data'!$E$2:$E$106)</x:f>
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="M7" s="63" t="n">
         <x:f>L7/105</x:f>
-        <x:v>0</x:v>
+        <x:v>0.01904761904761905</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -18741,18 +18591,18 @@
       </x:c>
       <x:c r="G8" s="20" t="n">
         <x:f>COUNTBLANK('Eligible Data'!$D$2:$D$106)</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="H8" s="63" t="n">
         <x:f>G8/105</x:f>
-        <x:v>0.009523809523809525</x:v>
+        <x:v>0.01904761904761905</x:v>
       </x:c>
       <x:c r="K8" s="20" t="str">
         <x:v>Valid responses</x:v>
       </x:c>
       <x:c r="L8" s="20" t="n">
         <x:f>SUM(L4:L6)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="M8" s="20"/>
     </x:row>
@@ -18770,7 +18620,7 @@
       </x:c>
       <x:c r="G9" s="20" t="n">
         <x:f>SUM(G4:G7)</x:f>
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H9" s="20"/>
       <x:c r="K9" s="20"/>
@@ -18787,7 +18637,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e8f60d87a7c4c5e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R334c39afcc554c4f"/>
 </x:worksheet>
 </file>
 
@@ -18841,11 +18691,11 @@
       </x:c>
       <x:c r="C4" s="64" t="n">
         <x:f>AVERAGE('Eligible Data'!AJ$2:AJ$106)</x:f>
-        <x:v>4.304761904761905</x:v>
+        <x:v>4.302588996763754</x:v>
       </x:c>
       <x:c r="D4" s="64" t="n">
         <x:f>STDEV.S('Eligible Data'!AJ$2:AJ$106)</x:f>
-        <x:v>0.7987895298917687</x:v>
+        <x:v>0.8022801020217095</x:v>
       </x:c>
       <x:c r="E4" s="20" t="n">
         <x:v>1</x:v>
@@ -18860,11 +18710,11 @@
       </x:c>
       <x:c r="C5" s="64" t="n">
         <x:f>AVERAGE('Eligible Data'!AK$2:AK$106)</x:f>
-        <x:v>4.238095238095239</x:v>
+        <x:v>4.237170596393898</x:v>
       </x:c>
       <x:c r="D5" s="64" t="n">
         <x:f>STDEV.S('Eligible Data'!AK$2:AK$106)</x:f>
-        <x:v>0.8401863688995214</x:v>
+        <x:v>0.847412887950359</x:v>
       </x:c>
       <x:c r="E5" s="20" t="n">
         <x:v>2</x:v>
@@ -18879,11 +18729,11 @@
       </x:c>
       <x:c r="C6" s="64" t="n">
         <x:f>AVERAGE('Eligible Data'!AI$2:AI$106)</x:f>
-        <x:v>4.165079365079365</x:v>
+        <x:v>4.161812297734628</x:v>
       </x:c>
       <x:c r="D6" s="64" t="n">
         <x:f>STDEV.S('Eligible Data'!AI$2:AI$106)</x:f>
-        <x:v>0.8531287434078472</x:v>
+        <x:v>0.8598577144162766</x:v>
       </x:c>
       <x:c r="E6" s="20" t="n">
         <x:v>3</x:v>
@@ -18898,11 +18748,11 @@
       </x:c>
       <x:c r="C7" s="64" t="n">
         <x:f>AVERAGE('Eligible Data'!AH$2:AH$106)</x:f>
-        <x:v>4.141949659863944</x:v>
+        <x:v>4.144244105409153</x:v>
       </x:c>
       <x:c r="D7" s="64" t="n">
         <x:f>STDEV.S('Eligible Data'!AH$2:AH$106)</x:f>
-        <x:v>0.8501443514838353</x:v>
+        <x:v>0.8528123907647945</x:v>
       </x:c>
       <x:c r="E7" s="20" t="n">
         <x:v>4</x:v>
@@ -18970,15 +18820,15 @@
       </x:c>
       <x:c r="D4" s="66" t="n">
         <x:f>COUNT('Eligible Data'!H$2:H$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E4" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!H$2:H$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.097087378640777</x:v>
       </x:c>
       <x:c r="F4" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!H$2:H$106)</x:f>
-        <x:v>0.9659969892034767</x:v>
+        <x:v>0.9652243781283479</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
@@ -18993,15 +18843,15 @@
       </x:c>
       <x:c r="D5" s="66" t="n">
         <x:f>COUNT('Eligible Data'!I$2:I$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E5" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!I$2:I$106)</x:f>
-        <x:v>3.9904761904761905</x:v>
+        <x:v>3.9805825242718447</x:v>
       </x:c>
       <x:c r="F5" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!I$2:I$106)</x:f>
-        <x:v>0.9353653964672975</x:v>
+        <x:v>0.9391337531780392</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -19016,15 +18866,15 @@
       </x:c>
       <x:c r="D6" s="66" t="n">
         <x:f>COUNT('Eligible Data'!J$2:J$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E6" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!J$2:J$106)</x:f>
-        <x:v>4.161904761904762</x:v>
+        <x:v>4.165048543689321</x:v>
       </x:c>
       <x:c r="F6" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!J$2:J$106)</x:f>
-        <x:v>0.9418048295673235</x:v>
+        <x:v>0.9507178647762545</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
@@ -19039,15 +18889,15 @@
       </x:c>
       <x:c r="D7" s="66" t="n">
         <x:f>COUNT('Eligible Data'!K$2:K$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E7" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!K$2:K$106)</x:f>
-        <x:v>4.180952380952381</x:v>
+        <x:v>4.184466019417476</x:v>
       </x:c>
       <x:c r="F7" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!K$2:K$106)</x:f>
-        <x:v>0.9070339699871346</x:v>
+        <x:v>0.9047540323911887</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
@@ -19062,15 +18912,15 @@
       </x:c>
       <x:c r="D8" s="66" t="n">
         <x:f>COUNT('Eligible Data'!L$2:L$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E8" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!L$2:L$106)</x:f>
-        <x:v>4.085714285714285</x:v>
+        <x:v>4.106796116504855</x:v>
       </x:c>
       <x:c r="F8" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!L$2:L$106)</x:f>
-        <x:v>1.0201271198528845</x:v>
+        <x:v>1.00890759559801</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
@@ -19085,15 +18935,15 @@
       </x:c>
       <x:c r="D9" s="66" t="n">
         <x:f>COUNT('Eligible Data'!M$2:M$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E9" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!M$2:M$106)</x:f>
-        <x:v>4.222219047619048</x:v>
+        <x:v>4.223300970873787</x:v>
       </x:c>
       <x:c r="F9" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!M$2:M$106)</x:f>
-        <x:v>0.9367489399816661</x:v>
+        <x:v>0.9386268530746252</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
@@ -19108,15 +18958,15 @@
       </x:c>
       <x:c r="D10" s="66" t="n">
         <x:f>COUNT('Eligible Data'!N$2:N$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E10" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!N$2:N$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="F10" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!N$2:N$106)</x:f>
-        <x:v>0.8990226683692459</x:v>
+        <x:v>0.9044383654516314</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
@@ -19131,15 +18981,15 @@
       </x:c>
       <x:c r="D11" s="66" t="n">
         <x:f>COUNT('Eligible Data'!O$2:O$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E11" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!O$2:O$106)</x:f>
-        <x:v>4.20952380952381</x:v>
+        <x:v>4.203883495145631</x:v>
       </x:c>
       <x:c r="F11" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!O$2:O$106)</x:f>
-        <x:v>0.89545044632939</x:v>
+        <x:v>0.9005360419017848</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
@@ -19154,15 +19004,15 @@
       </x:c>
       <x:c r="D12" s="66" t="n">
         <x:f>COUNT('Eligible Data'!P$2:P$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E12" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!P$2:P$106)</x:f>
-        <x:v>4.228571428571429</x:v>
+        <x:v>4.223300970873787</x:v>
       </x:c>
       <x:c r="F12" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!P$2:P$106)</x:f>
-        <x:v>0.922550216031031</x:v>
+        <x:v>0.9281231201599918</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
@@ -19177,15 +19027,15 @@
       </x:c>
       <x:c r="D13" s="66" t="n">
         <x:f>COUNT('Eligible Data'!Q$2:Q$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E13" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!Q$2:Q$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.097087378640777</x:v>
       </x:c>
       <x:c r="F13" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!Q$2:Q$106)</x:f>
-        <x:v>0.893607743103649</x:v>
+        <x:v>0.9022256044414432</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
@@ -19200,15 +19050,15 @@
       </x:c>
       <x:c r="D14" s="66" t="n">
         <x:f>COUNT('Eligible Data'!R$2:R$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E14" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!R$2:R$106)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>4.145631067961165</x:v>
       </x:c>
       <x:c r="F14" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!R$2:R$106)</x:f>
-        <x:v>0.9138735334633754</x:v>
+        <x:v>0.9225685264977033</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
@@ -19223,15 +19073,15 @@
       </x:c>
       <x:c r="D15" s="66" t="n">
         <x:f>COUNT('Eligible Data'!S$2:S$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E15" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!S$2:S$106)</x:f>
-        <x:v>4.219047619047619</x:v>
+        <x:v>4.213592233009709</x:v>
       </x:c>
       <x:c r="F15" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!S$2:S$106)</x:f>
-        <x:v>0.8985132204514343</x:v>
+        <x:v>0.9037013804554708</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
@@ -19246,15 +19096,15 @@
       </x:c>
       <x:c r="D16" s="66" t="n">
         <x:f>COUNT('Eligible Data'!T$2:T$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E16" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!T$2:T$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.087378640776699</x:v>
       </x:c>
       <x:c r="F16" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!T$2:T$106)</x:f>
-        <x:v>0.9759000729485324</x:v>
+        <x:v>0.9812636522492736</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
@@ -19269,15 +19119,15 @@
       </x:c>
       <x:c r="D17" s="66" t="n">
         <x:f>COUNT('Eligible Data'!U$2:U$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E17" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!U$2:U$106)</x:f>
-        <x:v>4.276190476190476</x:v>
+        <x:v>4.271844660194175</x:v>
       </x:c>
       <x:c r="F17" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!U$2:U$106)</x:f>
-        <x:v>0.9353653964672983</x:v>
+        <x:v>0.9413608709514449</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
@@ -19292,15 +19142,15 @@
       </x:c>
       <x:c r="D18" s="66" t="n">
         <x:f>COUNT('Eligible Data'!V$2:V$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E18" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!V$2:V$106)</x:f>
-        <x:v>4.295238095238095</x:v>
+        <x:v>4.29126213592233</x:v>
       </x:c>
       <x:c r="F18" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!V$2:V$106)</x:f>
-        <x:v>0.9085471234107099</x:v>
+        <x:v>0.9142774706598514</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
@@ -19315,15 +19165,15 @@
       </x:c>
       <x:c r="D19" s="66" t="n">
         <x:f>COUNT('Eligible Data'!W$2:W$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E19" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!W$2:W$106)</x:f>
-        <x:v>4.276190476190476</x:v>
+        <x:v>4.281553398058253</x:v>
       </x:c>
       <x:c r="F19" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!W$2:W$106)</x:f>
-        <x:v>0.8604028360559026</x:v>
+        <x:v>0.8565488863279861</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -19338,15 +19188,15 @@
       </x:c>
       <x:c r="D20" s="66" t="n">
         <x:f>COUNT('Eligible Data'!X$2:X$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E20" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!X$2:X$106)</x:f>
-        <x:v>4.3619047619047615</x:v>
+        <x:v>4.359223300970874</x:v>
       </x:c>
       <x:c r="F20" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!X$2:X$106)</x:f>
-        <x:v>0.7859806408338358</x:v>
+        <x:v>0.7903135259222531</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
@@ -19361,15 +19211,15 @@
       </x:c>
       <x:c r="D21" s="66" t="n">
         <x:f>COUNT('Eligible Data'!Y$2:Y$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E21" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!Y$2:Y$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="F21" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!Y$2:Y$106)</x:f>
-        <x:v>0.8773711983990704</x:v>
+        <x:v>0.8824925329011623</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
@@ -19384,15 +19234,15 @@
       </x:c>
       <x:c r="D22" s="66" t="n">
         <x:f>COUNT('Eligible Data'!Z$2:Z$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E22" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!Z$2:Z$106)</x:f>
-        <x:v>4.3619047619047615</x:v>
+        <x:v>4.359223300970874</x:v>
       </x:c>
       <x:c r="F22" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!Z$2:Z$106)</x:f>
-        <x:v>0.9000406991204664</x:v>
+        <x:v>0.9059105367685115</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
@@ -19407,15 +19257,15 @@
       </x:c>
       <x:c r="D23" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AA$2:AA$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E23" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AA$2:AA$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="F23" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AA$2:AA$106)</x:f>
-        <x:v>0.899022668369247</x:v>
+        <x:v>0.9044383654516324</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
@@ -19430,15 +19280,15 @@
       </x:c>
       <x:c r="D24" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AB$2:AB$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E24" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AB$2:AB$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.262135922330097</x:v>
       </x:c>
       <x:c r="F24" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AB$2:AB$106)</x:f>
-        <x:v>0.9096551695409252</x:v>
+        <x:v>0.9178103209626497</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
@@ -19453,15 +19303,15 @@
       </x:c>
       <x:c r="D25" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AC$2:AC$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E25" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AC$2:AC$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="F25" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AC$2:AC$106)</x:f>
-        <x:v>0.8607220752615163</x:v>
+        <x:v>0.8655031801251666</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
@@ -19476,15 +19326,15 @@
       </x:c>
       <x:c r="D26" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AD$2:AD$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E26" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AD$2:AD$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="F26" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AD$2:AD$106)</x:f>
-        <x:v>0.9148750390060583</x:v>
+        <x:v>0.9203993538095582</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
@@ -19499,15 +19349,15 @@
       </x:c>
       <x:c r="D27" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AE$2:AE$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E27" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AE$2:AE$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="F27" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AE$2:AE$106)</x:f>
-        <x:v>0.9043039133861845</x:v>
+        <x:v>0.9096851803540589</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
@@ -19522,15 +19372,15 @@
       </x:c>
       <x:c r="D28" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AF$2:AF$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E28" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AF$2:AF$106)</x:f>
-        <x:v>4.152380952380953</x:v>
+        <x:v>4.155339805825243</x:v>
       </x:c>
       <x:c r="F28" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AF$2:AF$106)</x:f>
-        <x:v>0.917573643879003</x:v>
+        <x:v>0.9262752899714672</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
@@ -19545,15 +19395,15 @@
       </x:c>
       <x:c r="D29" s="66" t="n">
         <x:f>COUNT('Eligible Data'!AG$2:AG$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E29" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!AG$2:AG$106)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.29126213592233</x:v>
       </x:c>
       <x:c r="F29" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!AG$2:AG$106)</x:f>
-        <x:v>0.9579052236951294</x:v>
+        <x:v>0.96640701003379</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19589,8 +19439,9 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="str">
-        <x:v>The non-category-imputed column records the one HL6 value imputed as 3.333 and is not assigned to a Likert category.</x:v>
-      </x:c>
+        <x:v>All five response categories contain the 103 analysed responses.</x:v>
+      </x:c>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="62" t="str">
@@ -19617,9 +19468,7 @@
       <x:c r="H3" s="62" t="str">
         <x:v>Strongly Agree</x:v>
       </x:c>
-      <x:c r="I3" s="62" t="str">
-        <x:v>Non-category imputed</x:v>
-      </x:c>
+      <x:c r="I3" s="62"/>
       <x:c r="J3" s="62" t="str">
         <x:v>Mean</x:v>
       </x:c>
@@ -19639,7 +19488,7 @@
       </x:c>
       <x:c r="C4" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$H$2:$H$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D4" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$H$2:$H$106,1)</x:f>
@@ -19651,7 +19500,7 @@
       </x:c>
       <x:c r="F4" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$H$2:$H$106,3)</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G4" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$H$2:$H$106,4)</x:f>
@@ -19659,21 +19508,18 @@
       </x:c>
       <x:c r="H4" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$H$2:$H$106,5)</x:f>
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I4" s="66" t="n">
-        <x:f>C4-SUM(D4:H4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I4" s="66"/>
       <x:c r="J4" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$H$2:$H$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.097087378640777</x:v>
       </x:c>
       <x:c r="K4" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$H$2:$H$106)</x:f>
-        <x:v>0.9659969892034767</x:v>
-      </x:c>
-      <x:c r="L4" s="25" t="str"/>
+        <x:v>0.9652243781283479</x:v>
+      </x:c>
+      <x:c r="L4" s="25"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="25" t="str">
@@ -19684,7 +19530,7 @@
       </x:c>
       <x:c r="C5" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$I$2:$I$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D5" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$I$2:$I$106,1)</x:f>
@@ -19700,25 +19546,22 @@
       </x:c>
       <x:c r="G5" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$I$2:$I$106,4)</x:f>
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H5" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$I$2:$I$106,5)</x:f>
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I5" s="66" t="n">
-        <x:f>C5-SUM(D5:H5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I5" s="66"/>
       <x:c r="J5" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$I$2:$I$106)</x:f>
-        <x:v>3.9904761904761905</x:v>
+        <x:v>3.9805825242718447</x:v>
       </x:c>
       <x:c r="K5" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$I$2:$I$106)</x:f>
-        <x:v>0.9353653964672975</x:v>
-      </x:c>
-      <x:c r="L5" s="25" t="str"/>
+        <x:v>0.9391337531780392</x:v>
+      </x:c>
+      <x:c r="L5" s="25"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="25" t="str">
@@ -19729,7 +19572,7 @@
       </x:c>
       <x:c r="C6" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$J$2:$J$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D6" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$J$2:$J$106,1)</x:f>
@@ -19745,25 +19588,22 @@
       </x:c>
       <x:c r="G6" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$J$2:$J$106,4)</x:f>
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H6" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$J$2:$J$106,5)</x:f>
         <x:v>42</x:v>
       </x:c>
-      <x:c r="I6" s="66" t="n">
-        <x:f>C6-SUM(D6:H6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I6" s="66"/>
       <x:c r="J6" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$J$2:$J$106)</x:f>
-        <x:v>4.161904761904762</x:v>
+        <x:v>4.165048543689321</x:v>
       </x:c>
       <x:c r="K6" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$J$2:$J$106)</x:f>
-        <x:v>0.9418048295673235</x:v>
-      </x:c>
-      <x:c r="L6" s="25" t="str"/>
+        <x:v>0.9507178647762545</x:v>
+      </x:c>
+      <x:c r="L6" s="25"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="25" t="str">
@@ -19774,7 +19614,7 @@
       </x:c>
       <x:c r="C7" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$K$2:$K$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D7" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$K$2:$K$106,1)</x:f>
@@ -19786,7 +19626,7 @@
       </x:c>
       <x:c r="F7" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$K$2:$K$106,3)</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G7" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$K$2:$K$106,4)</x:f>
@@ -19794,21 +19634,18 @@
       </x:c>
       <x:c r="H7" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$K$2:$K$106,5)</x:f>
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I7" s="66" t="n">
-        <x:f>C7-SUM(D7:H7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I7" s="66"/>
       <x:c r="J7" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$K$2:$K$106)</x:f>
-        <x:v>4.180952380952381</x:v>
+        <x:v>4.184466019417476</x:v>
       </x:c>
       <x:c r="K7" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$K$2:$K$106)</x:f>
-        <x:v>0.9070339699871346</x:v>
-      </x:c>
-      <x:c r="L7" s="25" t="str"/>
+        <x:v>0.9047540323911887</x:v>
+      </x:c>
+      <x:c r="L7" s="25"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="25" t="str">
@@ -19819,7 +19656,7 @@
       </x:c>
       <x:c r="C8" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$L$2:$L$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D8" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$L$2:$L$106,1)</x:f>
@@ -19827,7 +19664,7 @@
       </x:c>
       <x:c r="E8" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$L$2:$L$106,2)</x:f>
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F8" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$L$2:$L$106,3)</x:f>
@@ -19835,25 +19672,22 @@
       </x:c>
       <x:c r="G8" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$L$2:$L$106,4)</x:f>
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H8" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$L$2:$L$106,5)</x:f>
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I8" s="66" t="n">
-        <x:f>C8-SUM(D8:H8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I8" s="66"/>
       <x:c r="J8" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$L$2:$L$106)</x:f>
-        <x:v>4.085714285714285</x:v>
+        <x:v>4.106796116504855</x:v>
       </x:c>
       <x:c r="K8" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$L$2:$L$106)</x:f>
-        <x:v>1.0201271198528845</x:v>
-      </x:c>
-      <x:c r="L8" s="25" t="str"/>
+        <x:v>1.00890759559801</x:v>
+      </x:c>
+      <x:c r="L8" s="25"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="25" t="str">
@@ -19864,7 +19698,7 @@
       </x:c>
       <x:c r="C9" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$M$2:$M$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D9" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$M$2:$M$106,1)</x:f>
@@ -19884,23 +19718,18 @@
       </x:c>
       <x:c r="H9" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$M$2:$M$106,5)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I9" s="66" t="n">
-        <x:f>C9-SUM(D9:H9)</x:f>
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I9" s="66"/>
       <x:c r="J9" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$M$2:$M$106)</x:f>
-        <x:v>4.222219047619048</x:v>
+        <x:v>4.223300970873787</x:v>
       </x:c>
       <x:c r="K9" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$M$2:$M$106)</x:f>
-        <x:v>0.9367489399816661</x:v>
-      </x:c>
-      <x:c r="L9" s="25" t="str">
-        <x:v>One value = 3.333</x:v>
-      </x:c>
+        <x:v>0.9386268530746252</x:v>
+      </x:c>
+      <x:c r="L9" s="25"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="25" t="str">
@@ -19911,7 +19740,7 @@
       </x:c>
       <x:c r="C10" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$N$2:$N$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D10" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$N$2:$N$106,1)</x:f>
@@ -19927,25 +19756,22 @@
       </x:c>
       <x:c r="G10" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$N$2:$N$106,4)</x:f>
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$N$2:$N$106,5)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I10" s="66" t="n">
-        <x:f>C10-SUM(D10:H10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I10" s="66"/>
       <x:c r="J10" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$N$2:$N$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="K10" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$N$2:$N$106)</x:f>
-        <x:v>0.8990226683692459</x:v>
-      </x:c>
-      <x:c r="L10" s="25" t="str"/>
+        <x:v>0.9044383654516314</x:v>
+      </x:c>
+      <x:c r="L10" s="25"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="25" t="str">
@@ -19956,7 +19782,7 @@
       </x:c>
       <x:c r="C11" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$O$2:$O$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D11" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$O$2:$O$106,1)</x:f>
@@ -19972,25 +19798,22 @@
       </x:c>
       <x:c r="G11" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$O$2:$O$106,4)</x:f>
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$O$2:$O$106,5)</x:f>
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="I11" s="66" t="n">
-        <x:f>C11-SUM(D11:H11)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I11" s="66"/>
       <x:c r="J11" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$O$2:$O$106)</x:f>
-        <x:v>4.20952380952381</x:v>
+        <x:v>4.203883495145631</x:v>
       </x:c>
       <x:c r="K11" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$O$2:$O$106)</x:f>
-        <x:v>0.89545044632939</x:v>
-      </x:c>
-      <x:c r="L11" s="25" t="str"/>
+        <x:v>0.9005360419017848</x:v>
+      </x:c>
+      <x:c r="L11" s="25"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="25" t="str">
@@ -20001,7 +19824,7 @@
       </x:c>
       <x:c r="C12" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$P$2:$P$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D12" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$P$2:$P$106,1)</x:f>
@@ -20017,25 +19840,22 @@
       </x:c>
       <x:c r="G12" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$P$2:$P$106,4)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H12" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$P$2:$P$106,5)</x:f>
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I12" s="66" t="n">
-        <x:f>C12-SUM(D12:H12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I12" s="66"/>
       <x:c r="J12" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$P$2:$P$106)</x:f>
-        <x:v>4.228571428571429</x:v>
+        <x:v>4.223300970873787</x:v>
       </x:c>
       <x:c r="K12" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$P$2:$P$106)</x:f>
-        <x:v>0.922550216031031</x:v>
-      </x:c>
-      <x:c r="L12" s="25" t="str"/>
+        <x:v>0.9281231201599918</x:v>
+      </x:c>
+      <x:c r="L12" s="25"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="25" t="str">
@@ -20046,7 +19866,7 @@
       </x:c>
       <x:c r="C13" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$Q$2:$Q$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D13" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Q$2:$Q$106,1)</x:f>
@@ -20062,25 +19882,22 @@
       </x:c>
       <x:c r="G13" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Q$2:$Q$106,4)</x:f>
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H13" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Q$2:$Q$106,5)</x:f>
         <x:v>34</x:v>
       </x:c>
-      <x:c r="I13" s="66" t="n">
-        <x:f>C13-SUM(D13:H13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I13" s="66"/>
       <x:c r="J13" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$Q$2:$Q$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.097087378640777</x:v>
       </x:c>
       <x:c r="K13" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$Q$2:$Q$106)</x:f>
-        <x:v>0.893607743103649</x:v>
-      </x:c>
-      <x:c r="L13" s="25" t="str"/>
+        <x:v>0.9022256044414432</x:v>
+      </x:c>
+      <x:c r="L13" s="25"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="25" t="str">
@@ -20091,7 +19908,7 @@
       </x:c>
       <x:c r="C14" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$R$2:$R$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D14" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$R$2:$R$106,1)</x:f>
@@ -20107,25 +19924,22 @@
       </x:c>
       <x:c r="G14" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$R$2:$R$106,4)</x:f>
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H14" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$R$2:$R$106,5)</x:f>
         <x:v>38</x:v>
       </x:c>
-      <x:c r="I14" s="66" t="n">
-        <x:f>C14-SUM(D14:H14)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I14" s="66"/>
       <x:c r="J14" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$R$2:$R$106)</x:f>
-        <x:v>4.142857142857143</x:v>
+        <x:v>4.145631067961165</x:v>
       </x:c>
       <x:c r="K14" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$R$2:$R$106)</x:f>
-        <x:v>0.9138735334633754</x:v>
-      </x:c>
-      <x:c r="L14" s="25" t="str"/>
+        <x:v>0.9225685264977033</x:v>
+      </x:c>
+      <x:c r="L14" s="25"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="25" t="str">
@@ -20136,7 +19950,7 @@
       </x:c>
       <x:c r="C15" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$S$2:$S$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D15" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$S$2:$S$106,1)</x:f>
@@ -20152,25 +19966,22 @@
       </x:c>
       <x:c r="G15" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$S$2:$S$106,4)</x:f>
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H15" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$S$2:$S$106,5)</x:f>
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="I15" s="66" t="n">
-        <x:f>C15-SUM(D15:H15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="I15" s="66"/>
       <x:c r="J15" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$S$2:$S$106)</x:f>
-        <x:v>4.219047619047619</x:v>
+        <x:v>4.213592233009709</x:v>
       </x:c>
       <x:c r="K15" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$S$2:$S$106)</x:f>
-        <x:v>0.8985132204514343</x:v>
-      </x:c>
-      <x:c r="L15" s="25" t="str"/>
+        <x:v>0.9037013804554708</x:v>
+      </x:c>
+      <x:c r="L15" s="25"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="25" t="str">
@@ -20181,7 +19992,7 @@
       </x:c>
       <x:c r="C16" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$T$2:$T$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D16" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$T$2:$T$106,1)</x:f>
@@ -20197,25 +20008,22 @@
       </x:c>
       <x:c r="G16" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$T$2:$T$106,4)</x:f>
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H16" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$T$2:$T$106,5)</x:f>
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="I16" s="66" t="n">
-        <x:f>C16-SUM(D16:H16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I16" s="66"/>
       <x:c r="J16" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$T$2:$T$106)</x:f>
-        <x:v>4.095238095238095</x:v>
+        <x:v>4.087378640776699</x:v>
       </x:c>
       <x:c r="K16" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$T$2:$T$106)</x:f>
-        <x:v>0.9759000729485324</x:v>
-      </x:c>
-      <x:c r="L16" s="25" t="str"/>
+        <x:v>0.9812636522492736</x:v>
+      </x:c>
+      <x:c r="L16" s="25"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="25" t="str">
@@ -20226,7 +20034,7 @@
       </x:c>
       <x:c r="C17" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$U$2:$U$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D17" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$U$2:$U$106,1)</x:f>
@@ -20242,25 +20050,22 @@
       </x:c>
       <x:c r="G17" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$U$2:$U$106,4)</x:f>
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H17" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$U$2:$U$106,5)</x:f>
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I17" s="66" t="n">
-        <x:f>C17-SUM(D17:H17)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I17" s="66"/>
       <x:c r="J17" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$U$2:$U$106)</x:f>
-        <x:v>4.276190476190476</x:v>
+        <x:v>4.271844660194175</x:v>
       </x:c>
       <x:c r="K17" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$U$2:$U$106)</x:f>
-        <x:v>0.9353653964672983</x:v>
-      </x:c>
-      <x:c r="L17" s="25" t="str"/>
+        <x:v>0.9413608709514449</x:v>
+      </x:c>
+      <x:c r="L17" s="25"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="25" t="str">
@@ -20271,7 +20076,7 @@
       </x:c>
       <x:c r="C18" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$V$2:$V$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D18" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$V$2:$V$106,1)</x:f>
@@ -20287,25 +20092,22 @@
       </x:c>
       <x:c r="G18" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$V$2:$V$106,4)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H18" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$V$2:$V$106,5)</x:f>
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="I18" s="66" t="n">
-        <x:f>C18-SUM(D18:H18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I18" s="66"/>
       <x:c r="J18" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$V$2:$V$106)</x:f>
-        <x:v>4.295238095238095</x:v>
+        <x:v>4.29126213592233</x:v>
       </x:c>
       <x:c r="K18" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$V$2:$V$106)</x:f>
-        <x:v>0.9085471234107099</x:v>
-      </x:c>
-      <x:c r="L18" s="25" t="str"/>
+        <x:v>0.9142774706598514</x:v>
+      </x:c>
+      <x:c r="L18" s="25"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="25" t="str">
@@ -20316,7 +20118,7 @@
       </x:c>
       <x:c r="C19" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$W$2:$W$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D19" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$W$2:$W$106,1)</x:f>
@@ -20328,7 +20130,7 @@
       </x:c>
       <x:c r="F19" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$W$2:$W$106,3)</x:f>
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="G19" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$W$2:$W$106,4)</x:f>
@@ -20336,21 +20138,18 @@
       </x:c>
       <x:c r="H19" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$W$2:$W$106,5)</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I19" s="66" t="n">
-        <x:f>C19-SUM(D19:H19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I19" s="66"/>
       <x:c r="J19" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$W$2:$W$106)</x:f>
-        <x:v>4.276190476190476</x:v>
+        <x:v>4.281553398058253</x:v>
       </x:c>
       <x:c r="K19" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$W$2:$W$106)</x:f>
-        <x:v>0.8604028360559026</x:v>
-      </x:c>
-      <x:c r="L19" s="25" t="str"/>
+        <x:v>0.8565488863279861</x:v>
+      </x:c>
+      <x:c r="L19" s="25"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="25" t="str">
@@ -20361,7 +20160,7 @@
       </x:c>
       <x:c r="C20" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$X$2:$X$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D20" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$X$2:$X$106,1)</x:f>
@@ -20377,25 +20176,22 @@
       </x:c>
       <x:c r="G20" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$X$2:$X$106,4)</x:f>
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H20" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$X$2:$X$106,5)</x:f>
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="I20" s="66" t="n">
-        <x:f>C20-SUM(D20:H20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I20" s="66"/>
       <x:c r="J20" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$X$2:$X$106)</x:f>
-        <x:v>4.3619047619047615</x:v>
+        <x:v>4.359223300970874</x:v>
       </x:c>
       <x:c r="K20" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$X$2:$X$106)</x:f>
-        <x:v>0.7859806408338358</x:v>
-      </x:c>
-      <x:c r="L20" s="25" t="str"/>
+        <x:v>0.7903135259222531</x:v>
+      </x:c>
+      <x:c r="L20" s="25"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="25" t="str">
@@ -20406,7 +20202,7 @@
       </x:c>
       <x:c r="C21" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$Y$2:$Y$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D21" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Y$2:$Y$106,1)</x:f>
@@ -20422,25 +20218,22 @@
       </x:c>
       <x:c r="G21" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Y$2:$Y$106,4)</x:f>
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H21" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Y$2:$Y$106,5)</x:f>
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I21" s="66" t="n">
-        <x:f>C21-SUM(D21:H21)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I21" s="66"/>
       <x:c r="J21" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$Y$2:$Y$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="K21" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$Y$2:$Y$106)</x:f>
-        <x:v>0.8773711983990704</x:v>
-      </x:c>
-      <x:c r="L21" s="25" t="str"/>
+        <x:v>0.8824925329011623</x:v>
+      </x:c>
+      <x:c r="L21" s="25"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="25" t="str">
@@ -20451,7 +20244,7 @@
       </x:c>
       <x:c r="C22" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$Z$2:$Z$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D22" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Z$2:$Z$106,1)</x:f>
@@ -20467,25 +20260,22 @@
       </x:c>
       <x:c r="G22" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Z$2:$Z$106,4)</x:f>
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H22" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$Z$2:$Z$106,5)</x:f>
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I22" s="66" t="n">
-        <x:f>C22-SUM(D22:H22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I22" s="66"/>
       <x:c r="J22" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$Z$2:$Z$106)</x:f>
-        <x:v>4.3619047619047615</x:v>
+        <x:v>4.359223300970874</x:v>
       </x:c>
       <x:c r="K22" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$Z$2:$Z$106)</x:f>
-        <x:v>0.9000406991204664</x:v>
-      </x:c>
-      <x:c r="L22" s="25" t="str"/>
+        <x:v>0.9059105367685115</x:v>
+      </x:c>
+      <x:c r="L22" s="25"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="25" t="str">
@@ -20496,7 +20286,7 @@
       </x:c>
       <x:c r="C23" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AA$2:$AA$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D23" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AA$2:$AA$106,1)</x:f>
@@ -20512,25 +20302,22 @@
       </x:c>
       <x:c r="G23" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AA$2:$AA$106,4)</x:f>
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H23" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AA$2:$AA$106,5)</x:f>
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="I23" s="66" t="n">
-        <x:f>C23-SUM(D23:H23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I23" s="66"/>
       <x:c r="J23" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AA$2:$AA$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.252427184466019</x:v>
       </x:c>
       <x:c r="K23" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AA$2:$AA$106)</x:f>
-        <x:v>0.899022668369247</x:v>
-      </x:c>
-      <x:c r="L23" s="25" t="str"/>
+        <x:v>0.9044383654516324</x:v>
+      </x:c>
+      <x:c r="L23" s="25"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="25" t="str">
@@ -20541,7 +20328,7 @@
       </x:c>
       <x:c r="C24" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AB$2:$AB$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D24" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AB$2:$AB$106,1)</x:f>
@@ -20557,25 +20344,22 @@
       </x:c>
       <x:c r="G24" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AB$2:$AB$106,4)</x:f>
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H24" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AB$2:$AB$106,5)</x:f>
         <x:v>49</x:v>
       </x:c>
-      <x:c r="I24" s="66" t="n">
-        <x:f>C24-SUM(D24:H24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I24" s="66"/>
       <x:c r="J24" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AB$2:$AB$106)</x:f>
-        <x:v>4.257142857142857</x:v>
+        <x:v>4.262135922330097</x:v>
       </x:c>
       <x:c r="K24" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AB$2:$AB$106)</x:f>
-        <x:v>0.9096551695409252</x:v>
-      </x:c>
-      <x:c r="L24" s="25" t="str"/>
+        <x:v>0.9178103209626497</x:v>
+      </x:c>
+      <x:c r="L24" s="25"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="25" t="str">
@@ -20586,7 +20370,7 @@
       </x:c>
       <x:c r="C25" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AC$2:$AC$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D25" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AC$2:$AC$106,1)</x:f>
@@ -20602,25 +20386,22 @@
       </x:c>
       <x:c r="G25" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AC$2:$AC$106,4)</x:f>
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="H25" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AC$2:$AC$106,5)</x:f>
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I25" s="66" t="n">
-        <x:f>C25-SUM(D25:H25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="I25" s="66"/>
       <x:c r="J25" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AC$2:$AC$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="K25" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AC$2:$AC$106)</x:f>
-        <x:v>0.8607220752615163</x:v>
-      </x:c>
-      <x:c r="L25" s="25" t="str"/>
+        <x:v>0.8655031801251666</x:v>
+      </x:c>
+      <x:c r="L25" s="25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="25" t="str">
@@ -20631,7 +20412,7 @@
       </x:c>
       <x:c r="C26" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AD$2:$AD$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D26" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AD$2:$AD$106,1)</x:f>
@@ -20647,25 +20428,22 @@
       </x:c>
       <x:c r="G26" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AD$2:$AD$106,4)</x:f>
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H26" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AD$2:$AD$106,5)</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I26" s="66" t="n">
-        <x:f>C26-SUM(D26:H26)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I26" s="66"/>
       <x:c r="J26" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AD$2:$AD$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="K26" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AD$2:$AD$106)</x:f>
-        <x:v>0.9148750390060583</x:v>
-      </x:c>
-      <x:c r="L26" s="25" t="str"/>
+        <x:v>0.9203993538095582</x:v>
+      </x:c>
+      <x:c r="L26" s="25"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="25" t="str">
@@ -20676,7 +20454,7 @@
       </x:c>
       <x:c r="C27" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AE$2:$AE$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D27" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AE$2:$AE$106,1)</x:f>
@@ -20692,25 +20470,22 @@
       </x:c>
       <x:c r="G27" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AE$2:$AE$106,4)</x:f>
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H27" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AE$2:$AE$106,5)</x:f>
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="I27" s="66" t="n">
-        <x:f>C27-SUM(D27:H27)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="I27" s="66"/>
       <x:c r="J27" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AE$2:$AE$106)</x:f>
-        <x:v>4.238095238095238</x:v>
+        <x:v>4.233009708737864</x:v>
       </x:c>
       <x:c r="K27" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AE$2:$AE$106)</x:f>
-        <x:v>0.9043039133861845</x:v>
-      </x:c>
-      <x:c r="L27" s="25" t="str"/>
+        <x:v>0.9096851803540589</x:v>
+      </x:c>
+      <x:c r="L27" s="25"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="25" t="str">
@@ -20721,7 +20496,7 @@
       </x:c>
       <x:c r="C28" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AF$2:$AF$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D28" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AF$2:$AF$106,1)</x:f>
@@ -20737,25 +20512,22 @@
       </x:c>
       <x:c r="G28" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AF$2:$AF$106,4)</x:f>
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="H28" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AF$2:$AF$106,5)</x:f>
         <x:v>40</x:v>
       </x:c>
-      <x:c r="I28" s="66" t="n">
-        <x:f>C28-SUM(D28:H28)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I28" s="66"/>
       <x:c r="J28" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AF$2:$AF$106)</x:f>
-        <x:v>4.152380952380953</x:v>
+        <x:v>4.155339805825243</x:v>
       </x:c>
       <x:c r="K28" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AF$2:$AF$106)</x:f>
-        <x:v>0.917573643879003</x:v>
-      </x:c>
-      <x:c r="L28" s="25" t="str"/>
+        <x:v>0.9262752899714672</x:v>
+      </x:c>
+      <x:c r="L28" s="25"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="25" t="str">
@@ -20766,7 +20538,7 @@
       </x:c>
       <x:c r="C29" s="66" t="n">
         <x:f>COUNT('Eligible Data'!$AG$2:$AG$106)</x:f>
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D29" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AG$2:$AG$106,1)</x:f>
@@ -20782,25 +20554,22 @@
       </x:c>
       <x:c r="G29" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AG$2:$AG$106,4)</x:f>
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H29" s="66" t="n">
         <x:f>COUNTIF('Eligible Data'!$AG$2:$AG$106,5)</x:f>
         <x:v>55</x:v>
       </x:c>
-      <x:c r="I29" s="66" t="n">
-        <x:f>C29-SUM(D29:H29)</x:f>
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I29" s="66"/>
       <x:c r="J29" s="67" t="n">
         <x:f>AVERAGE('Eligible Data'!$AG$2:$AG$106)</x:f>
-        <x:v>4.285714285714286</x:v>
+        <x:v>4.29126213592233</x:v>
       </x:c>
       <x:c r="K29" s="67" t="n">
         <x:f>STDEV.S('Eligible Data'!$AG$2:$AG$106)</x:f>
-        <x:v>0.9579052236951294</x:v>
-      </x:c>
-      <x:c r="L29" s="25" t="str"/>
+        <x:v>0.96640701003379</x:v>
+      </x:c>
+      <x:c r="L29" s="25"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
